--- a/QSTL_MicroDSUB_FFC/CPL.xlsx
+++ b/QSTL_MicroDSUB_FFC/CPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jeonghyun\SNU_GIT\QSTL_MicroDSUB_FFC\QSTL_MicroDSUB_FFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27726CE2-E2D1-43CC-9E59-09C3037415B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86317808-D2E6-4F34-9310-6C8AC7698B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="0" windowWidth="12800" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="6640" windowWidth="19200" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Designator</t>
   </si>
@@ -50,46 +50,19 @@
     <t>Rotation</t>
   </si>
   <si>
-    <t>J6</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
     <t>TOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.975mm</t>
+    <t>2.275mm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13mm</t>
+    <t>29mm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>25mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>31mm</t>
+    <t>J1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,17 +463,17 @@
       <c r="T1" s="2"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>5</v>
+      <c r="A2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>270</v>
@@ -510,75 +483,21 @@
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>270</v>
-      </c>
       <c r="S3" s="1"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>270</v>
-      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
       <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <v>270</v>
-      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>270</v>
-      </c>
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
